--- a/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MBLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>MBLY</t>
   </si>
@@ -656,338 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44464</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44282</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44191</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E8" s="3">
         <v>558000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>446000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>504000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>506000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>438000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>490000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>486000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>439000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>239000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>637000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>530000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>454000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>458000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>565000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>450000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>460000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>394000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>356000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>326000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>327000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>377000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>334000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>231000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E9" s="3">
         <v>283000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>244000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>261000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>254000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>231000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>249000</v>
       </c>
       <c r="J9" s="3">
         <v>249000</v>
       </c>
       <c r="K9" s="3">
+        <v>249000</v>
+      </c>
+      <c r="L9" s="3">
         <v>230000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>185000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>293000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>258000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>230000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>251000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>265000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>233000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>231000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>218000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>202000</v>
-      </c>
-      <c r="V9" s="3">
-        <v>173000</v>
       </c>
       <c r="W9" s="3">
         <v>173000</v>
       </c>
       <c r="X9" s="3">
+        <v>173000</v>
+      </c>
+      <c r="Y9" s="3">
         <v>183000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>176000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E10" s="3">
         <v>275000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>202000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>243000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>252000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>207000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>241000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>237000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>209000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>54000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>344000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>272000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>224000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>207000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>300000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>217000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>229000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>176000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>154000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>153000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>154000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>194000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>158000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>76000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E12" s="3">
         <v>323000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>290000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>304000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>282000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>275000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>281000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>303000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>256000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>243000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>225000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>218000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>211000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>235000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>224000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>206000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>179000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>180000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>154000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>132000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>128000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>130000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>128000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1162,17 +1179,20 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
         <v>3788000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1182,15 +1202,15 @@
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>2695000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1206,8 +1226,8 @@
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1236,16 +1256,19 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E15" s="3">
         <v>38000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>35000</v>
       </c>
       <c r="F15" s="3">
         <v>35000</v>
@@ -1257,7 +1280,7 @@
         <v>35000</v>
       </c>
       <c r="I15" s="3">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="J15" s="3">
         <v>33000</v>
@@ -1266,29 +1289,29 @@
         <v>33000</v>
       </c>
       <c r="L15" s="3">
+        <v>33000</v>
+      </c>
+      <c r="M15" s="3">
         <v>31000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>26000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>17000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1298,8 +1321,8 @@
       <c r="V15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>538000</v>
+      </c>
+      <c r="E17" s="3">
         <v>666000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>586000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>613000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>580000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>555000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>576000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>598000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>533000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>477000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>564000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>522000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>487000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>539000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>541000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>475000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>450000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>440000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>346000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>342000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>355000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>345000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-108000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-140000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-109000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-74000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-117000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-86000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-112000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-94000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-238000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>73000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-46000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-44000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-20000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>22000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1511,8 +1544,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1540,127 +1574,133 @@
       <c r="K20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="3">
         <v>-17000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-15000</v>
       </c>
       <c r="O20" s="3">
         <v>-15000</v>
       </c>
       <c r="P20" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-70000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-105000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-74000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-39000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-82000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-53000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-79000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-61000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-190000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>116000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>49000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>175000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>119000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>480000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>237000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1703,15 +1743,15 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="3">
         <v>4000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11000</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1727,162 +1767,171 @@
       <c r="X22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3882000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-125000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-92000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-61000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-99000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-68000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2793000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-81000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-221000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>84000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>34000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-30000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-44000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-46000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-20000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-64000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>3000</v>
       </c>
       <c r="I24" s="3">
         <v>3000</v>
       </c>
       <c r="J24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K24" s="3">
         <v>-78000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>15000</v>
       </c>
       <c r="S24" s="3">
         <v>15000</v>
       </c>
       <c r="T24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="U24" s="3">
         <v>16000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>6000</v>
       </c>
       <c r="W24" s="3">
         <v>6000</v>
       </c>
       <c r="X24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3818000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-127000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-96000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-67000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-102000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-71000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2715000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-86000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-218000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-60000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-53000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-26000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-21000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3818000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-127000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-96000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-67000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-102000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-71000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2715000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-86000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-218000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>63000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>17000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-60000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-53000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-26000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-21000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>25000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,8 +2466,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2428,127 +2498,133 @@
       <c r="K32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="3">
         <v>17000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>15000</v>
       </c>
       <c r="O32" s="3">
         <v>15000</v>
       </c>
       <c r="P32" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Q32" s="3">
         <v>8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3818000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-127000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-96000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-67000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-102000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-71000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2715000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-86000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-218000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>63000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>17000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-60000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-53000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-26000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>25000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3818000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-127000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-96000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-67000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-102000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-71000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2715000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-86000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-218000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>63000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>17000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-60000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-53000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-26000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>25000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44464</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44282</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44191</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,62 +2916,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1311000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1211000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1836000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1749000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1709000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1512000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1426000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1293000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1203000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1223000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1212000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1193000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1142000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1161000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1024000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>871000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>774000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2904,17 +2991,20 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E42" s="3">
         <v>133000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2922,17 +3012,17 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>44000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2978,62 +3068,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E43" s="3">
         <v>226000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>131000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>201000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>217000</v>
       </c>
       <c r="H43" s="3">
         <v>217000</v>
       </c>
       <c r="I43" s="3">
+        <v>217000</v>
+      </c>
+      <c r="J43" s="3">
         <v>212000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>223000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>204000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>120000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>357000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>281000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>240000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>239000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>269000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1123000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1115000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3052,62 +3145,65 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E44" s="3">
         <v>303000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>327000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>318000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>325000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>364000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>415000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>457000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>485000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>456000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>391000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>354000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>263000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>173000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>113000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>105000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>98000</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3126,8 +3222,11 @@
       <c r="Z44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3135,53 +3234,53 @@
         <v>120000</v>
       </c>
       <c r="E45" s="3">
+        <v>120000</v>
+      </c>
+      <c r="F45" s="3">
         <v>184000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>148000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>146000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>78000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>121000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>116000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>115000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>132000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>106000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>80000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>82000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>110000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>63000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>56000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3200,62 +3299,65 @@
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2081000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1993000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2478000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2416000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2397000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2215000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2174000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2099000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2007000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1931000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2066000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1908000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1717000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1655000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1516000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2162000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2043000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3274,8 +3376,11 @@
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3291,12 +3396,12 @@
       <c r="G47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3">
         <v>10000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3318,8 +3423,8 @@
       <c r="P47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3348,62 +3453,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E48" s="3">
         <v>468000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>523000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>453000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>454000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>450000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>505000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>461000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>456000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>454000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>496000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>426000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>422000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>401000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>384000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>354000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>338000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3422,62 +3530,65 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5978000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6092000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9366000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9476000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9587000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9698000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9809000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9920000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12726000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12837000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12948000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13060000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13171000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13289000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13422000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13553000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13684000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,62 +3761,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E52" s="3">
         <v>182000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>125000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>135000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>140000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>125000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>91000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>123000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>118000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>120000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>67000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>111000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>120000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>117000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>119000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>95000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>97000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,62 +3915,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8838000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8735000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12492000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12480000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12578000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12498000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12579000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12603000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15307000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15342000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15577000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15505000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15430000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15462000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15441000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16164000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16162000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,62 +4052,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>228000</v>
+        <v>251000</v>
       </c>
       <c r="E57" s="3">
         <v>228000</v>
       </c>
       <c r="F57" s="3">
+        <v>228000</v>
+      </c>
+      <c r="G57" s="3">
         <v>211000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>199000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>150000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>190000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>166000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>171000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>166000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>229000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>221000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>208000</v>
       </c>
       <c r="P57" s="3">
         <v>208000</v>
       </c>
       <c r="Q57" s="3">
+        <v>208000</v>
+      </c>
+      <c r="R57" s="3">
         <v>189000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>160000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>138000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4005,11 +4139,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>18000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -4017,23 +4151,23 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>13000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
       </c>
       <c r="L58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -4070,62 +4204,65 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E59" s="3">
         <v>54000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>38000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>33000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>82000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>91000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>86000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>116000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>195000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4620000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4592000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4144,62 +4281,65 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>452000</v>
+      </c>
+      <c r="E60" s="3">
         <v>419000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>406000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>374000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>347000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>290000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>333000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>362000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>346000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>329000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>403000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>391000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>381000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>418000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>384000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4780000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4730000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4218,53 +4358,56 @@
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E61" s="3">
         <v>62000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>53000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>39000</v>
       </c>
       <c r="N61" s="3">
         <v>39000</v>
       </c>
       <c r="O61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="P61" s="3">
         <v>42000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4292,62 +4435,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3">
         <v>7000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>4000</v>
       </c>
       <c r="G62" s="3">
         <v>4000</v>
       </c>
       <c r="H62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="3">
         <v>7000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R62" s="3">
         <v>263000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>224000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>233000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,62 +4743,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>628000</v>
+      </c>
+      <c r="E66" s="3">
         <v>571000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>611000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>545000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>512000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>449000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>492000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>525000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>588000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>579000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>653000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>632000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>630000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>675000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>647000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5004000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4963000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,62 +5157,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7291000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7270000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3452000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3325000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3229000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3162000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3060000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2989000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-274000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-188000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-50000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>57000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11178000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11223000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,62 +5465,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8210000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8164000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11881000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11935000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12066000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12049000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12087000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12078000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14719000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14763000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14924000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14873000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14800000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14787000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14794000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11160000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11199000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44464</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44282</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44191</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3818000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-127000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-96000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-67000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-102000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-71000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2715000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-86000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-218000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>63000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>17000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-60000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-53000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-26000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>25000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5620,7 +5819,7 @@
         <v>18000</v>
       </c>
       <c r="E83" s="3">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="F83" s="3">
         <v>16000</v>
@@ -5629,50 +5828,50 @@
         <v>16000</v>
       </c>
       <c r="H83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I83" s="3">
         <v>14000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>5000</v>
       </c>
       <c r="P83" s="3">
         <v>5000</v>
       </c>
       <c r="Q83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="R83" s="3">
         <v>137000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>138000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V83" s="3">
         <v>526000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5685,8 +5884,11 @@
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,68 +6269,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E89" s="3">
         <v>75000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>113000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>167000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>213000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>109000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>204000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>126000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>109000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>171000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>151000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>162000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V89" s="3">
         <v>599000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6129,8 +6346,11 @@
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,70 +6377,71 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-14000</v>
       </c>
       <c r="H91" s="3">
         <v>-14000</v>
       </c>
       <c r="I91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-13000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-53000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>16</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>16</v>
@@ -6231,8 +6452,11 @@
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,68 +6606,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-699000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>868000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-25000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V94" s="3">
         <v>-157000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6453,8 +6683,11 @@
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6525,8 +6759,8 @@
       <c r="P96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,68 +7020,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-50000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-71000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-866000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V100" s="3">
         <v>91000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6851,68 +7097,71 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>16</v>
       </c>
@@ -6925,68 +7174,71 @@
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-622000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>91000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>202000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>89000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>132000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>90000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>50000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>138000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>153000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>98000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V102" s="3">
         <v>532000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6997,6 +7249,9 @@
         <v>16</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
